--- a/data-collection/tomcat-data.xlsx
+++ b/data-collection/tomcat-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politechnikawroclawska-my.sharepoint.com/personal/260364_student_pwr_edu_pl/Documents/Semestr10-3mgr/dyplomowe/ai/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politechnikawroclawska-my.sharepoint.com/personal/260364_student_pwr_edu_pl/Documents/Semestr10-3mgr/dyplomowe/ai/data-collection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC1048A6391B61545ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE9CF9E1-1F72-41B4-B353-44E2571593FC}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_F25DC773A252ABDACC1048A6391B61545ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{077BDB52-6692-47E0-A630-042ADEB6EE4C}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="-11640" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="573">
   <si>
     <t>Wersja</t>
   </si>
@@ -1023,12 +1023,747 @@
   </si>
   <si>
     <t>Mediana</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Nov 11, 2024</t>
+  </si>
+  <si>
+    <t>Oct 09, 2024</t>
+  </si>
+  <si>
+    <t>Sep 17, 2024</t>
+  </si>
+  <si>
+    <t>Sep 10, 2024</t>
+  </si>
+  <si>
+    <t>Aug 06, 2024</t>
+  </si>
+  <si>
+    <t>Jul 12, 2024</t>
+  </si>
+  <si>
+    <t>Jun 19, 2024</t>
+  </si>
+  <si>
+    <t>May 13, 2024</t>
+  </si>
+  <si>
+    <t>Apr 23, 2024</t>
+  </si>
+  <si>
+    <t>Mar 26, 2024</t>
+  </si>
+  <si>
+    <t>Feb 19, 2024</t>
+  </si>
+  <si>
+    <t>Jan 09, 2024</t>
+  </si>
+  <si>
+    <t>Dec 12, 2023</t>
+  </si>
+  <si>
+    <t>Nov 15, 2023</t>
+  </si>
+  <si>
+    <t>Oct 16, 2023</t>
+  </si>
+  <si>
+    <t>Oct 10, 2023</t>
+  </si>
+  <si>
+    <t>Aug 25, 2023</t>
+  </si>
+  <si>
+    <t>Aug 14, 2023</t>
+  </si>
+  <si>
+    <t>Jul 10, 2023</t>
+  </si>
+  <si>
+    <t>Jun 12, 2023</t>
+  </si>
+  <si>
+    <t>May 20, 2023</t>
+  </si>
+  <si>
+    <t>Apr 19, 2023</t>
+  </si>
+  <si>
+    <t>Mar 04, 2023</t>
+  </si>
+  <si>
+    <t>Feb 24, 2023</t>
+  </si>
+  <si>
+    <t>Jan 13, 2023</t>
+  </si>
+  <si>
+    <t>Dec 05, 2022</t>
+  </si>
+  <si>
+    <t>Nov 14, 2022</t>
+  </si>
+  <si>
+    <t>Oct 11, 2022</t>
+  </si>
+  <si>
+    <t>Sep 26, 2022</t>
+  </si>
+  <si>
+    <t>Oct 10, 2022</t>
+  </si>
+  <si>
+    <t>Sep 27, 2022</t>
+  </si>
+  <si>
+    <t>Jul 26, 2022</t>
+  </si>
+  <si>
+    <t>Jun 11, 2022</t>
+  </si>
+  <si>
+    <t>May 16, 2022</t>
+  </si>
+  <si>
+    <t>Apr 02, 2022</t>
+  </si>
+  <si>
+    <t>Mar 14, 2022</t>
+  </si>
+  <si>
+    <t>Feb 28, 2022</t>
+  </si>
+  <si>
+    <t>Jan 20, 2022</t>
+  </si>
+  <si>
+    <t>Dec 08, 2021</t>
+  </si>
+  <si>
+    <t>Nov 15, 2021</t>
+  </si>
+  <si>
+    <t>Oct 01, 2021</t>
+  </si>
+  <si>
+    <t>Sep 10, 2021</t>
+  </si>
+  <si>
+    <t>Aug 05, 2021</t>
+  </si>
+  <si>
+    <t>Jul 05, 2021</t>
+  </si>
+  <si>
+    <t>Jun 15, 2021</t>
+  </si>
+  <si>
+    <t>May 13, 2021</t>
+  </si>
+  <si>
+    <t>Apr 06, 2021</t>
+  </si>
+  <si>
+    <t>Mar 10, 2021</t>
+  </si>
+  <si>
+    <t>Feb 02, 2021</t>
+  </si>
+  <si>
+    <t>Dec 08, 2020</t>
+  </si>
+  <si>
+    <t>Dec 09, 2024</t>
+  </si>
+  <si>
+    <t>Nov 09, 2024</t>
+  </si>
+  <si>
+    <t>Oct 08, 2024</t>
+  </si>
+  <si>
+    <t>Jul 08, 2024</t>
+  </si>
+  <si>
+    <t>May 07, 2024</t>
+  </si>
+  <si>
+    <t>Apr 16, 2024</t>
+  </si>
+  <si>
+    <t>Mar 15, 2024</t>
+  </si>
+  <si>
+    <t>Oct 13, 2023</t>
+  </si>
+  <si>
+    <t>Aug 15, 2023</t>
+  </si>
+  <si>
+    <t>Jun 09, 2023</t>
+  </si>
+  <si>
+    <t>May 10, 2023</t>
+  </si>
+  <si>
+    <t>Apr 18, 2023</t>
+  </si>
+  <si>
+    <t>Mar 03, 2023</t>
+  </si>
+  <si>
+    <t>Feb 23, 2023</t>
+  </si>
+  <si>
+    <t>Dec 01, 2022</t>
+  </si>
+  <si>
+    <t>Oct 07, 2022</t>
+  </si>
+  <si>
+    <t>Jul 20, 2022</t>
+  </si>
+  <si>
+    <t>Jun 09, 2022</t>
+  </si>
+  <si>
+    <t>Oct 02, 2021</t>
+  </si>
+  <si>
+    <t>Aug 06, 2021</t>
+  </si>
+  <si>
+    <t>Jul 02, 2021</t>
+  </si>
+  <si>
+    <t>Nov 17, 2020</t>
+  </si>
+  <si>
+    <t>Oct 09, 2020</t>
+  </si>
+  <si>
+    <t>Sep 15, 2020</t>
+  </si>
+  <si>
+    <t>Jul 05, 2020</t>
+  </si>
+  <si>
+    <t>Jun 07, 2020</t>
+  </si>
+  <si>
+    <t>May 11, 2020</t>
+  </si>
+  <si>
+    <t>Apr 08, 2020</t>
+  </si>
+  <si>
+    <t>Mar 16, 2020</t>
+  </si>
+  <si>
+    <t>Feb 11, 2020</t>
+  </si>
+  <si>
+    <t>Dec 07, 2019</t>
+  </si>
+  <si>
+    <t>Nov 16, 2019</t>
+  </si>
+  <si>
+    <t>Oct 07, 2019</t>
+  </si>
+  <si>
+    <t>Sep 16, 2019</t>
+  </si>
+  <si>
+    <t>Aug 17, 2019</t>
+  </si>
+  <si>
+    <t>Jul 09, 2019</t>
+  </si>
+  <si>
+    <t>Jun 08, 2019</t>
+  </si>
+  <si>
+    <t>May 15, 2019</t>
+  </si>
+  <si>
+    <t>Apr 14, 2019</t>
+  </si>
+  <si>
+    <t>Mar 19, 2019</t>
+  </si>
+  <si>
+    <t>Feb 08, 2019</t>
+  </si>
+  <si>
+    <t>Dec 12, 2018</t>
+  </si>
+  <si>
+    <t>Nov 02, 2018</t>
+  </si>
+  <si>
+    <t>Sep 10, 2018</t>
+  </si>
+  <si>
+    <t>Aug 11, 2018</t>
+  </si>
+  <si>
+    <t>Jun 20, 2018</t>
+  </si>
+  <si>
+    <t>Apr 27, 2018</t>
+  </si>
+  <si>
+    <t>Apr 03, 2018</t>
+  </si>
+  <si>
+    <t>Mar 05, 2018</t>
+  </si>
+  <si>
+    <t>Feb 06, 2018</t>
+  </si>
+  <si>
+    <t>Jan 18, 2018</t>
+  </si>
+  <si>
+    <t>Nov 25, 2017</t>
+  </si>
+  <si>
+    <t>Sep 27, 2017</t>
+  </si>
+  <si>
+    <t>Jan 19, 2023</t>
+  </si>
+  <si>
+    <t>Nov 22, 2022</t>
+  </si>
+  <si>
+    <t>Aug 13, 2022</t>
+  </si>
+  <si>
+    <t>May 24, 2022</t>
+  </si>
+  <si>
+    <t>Mar 17, 2022</t>
+  </si>
+  <si>
+    <t>Mar 01, 2022</t>
+  </si>
+  <si>
+    <t>Nov 17, 2021</t>
+  </si>
+  <si>
+    <t>Oct 06, 2021</t>
+  </si>
+  <si>
+    <t>Sep 13, 2021</t>
+  </si>
+  <si>
+    <t>Aug 16, 2021</t>
+  </si>
+  <si>
+    <t>Jun 16, 2021</t>
+  </si>
+  <si>
+    <t>Feb 03, 2021</t>
+  </si>
+  <si>
+    <t>Nov 17, 2019</t>
+  </si>
+  <si>
+    <t>Oct 12, 2019</t>
+  </si>
+  <si>
+    <t>Aug 21, 2019</t>
+  </si>
+  <si>
+    <t>Apr 12, 2019</t>
+  </si>
+  <si>
+    <t>Mar 20, 2019</t>
+  </si>
+  <si>
+    <t>Dec 18, 2018</t>
+  </si>
+  <si>
+    <t>Nov 08, 2018</t>
+  </si>
+  <si>
+    <t>Aug 12, 2018</t>
+  </si>
+  <si>
+    <t>Nov 27, 2017</t>
+  </si>
+  <si>
+    <t>Sep 28, 2017</t>
+  </si>
+  <si>
+    <t>Sep 13, 2017</t>
+  </si>
+  <si>
+    <t>Aug 02, 2017</t>
+  </si>
+  <si>
+    <t>Jul 24, 2017</t>
+  </si>
+  <si>
+    <t>Jun 21, 2017</t>
+  </si>
+  <si>
+    <t>May 05, 2017</t>
+  </si>
+  <si>
+    <t>Apr 13, 2017</t>
+  </si>
+  <si>
+    <t>Mar 27, 2017</t>
+  </si>
+  <si>
+    <t>Mar 08, 2017</t>
+  </si>
+  <si>
+    <t>Jan 10, 2017</t>
+  </si>
+  <si>
+    <t>Dec 05, 2016</t>
+  </si>
+  <si>
+    <t>Nov 03, 2016</t>
+  </si>
+  <si>
+    <t>Oct 06, 2016</t>
+  </si>
+  <si>
+    <t>Aug 31, 2016</t>
+  </si>
+  <si>
+    <t>Jul 06, 2016</t>
+  </si>
+  <si>
+    <t>Jun 09, 2016</t>
+  </si>
+  <si>
+    <t>May 11, 2016</t>
+  </si>
+  <si>
+    <t>Mar 17, 2016</t>
+  </si>
+  <si>
+    <t>Jun 29, 2018</t>
+  </si>
+  <si>
+    <t>Apr 28, 2018</t>
+  </si>
+  <si>
+    <t>Apr 09, 2018</t>
+  </si>
+  <si>
+    <t>Feb 07, 2018</t>
+  </si>
+  <si>
+    <t>Jan 19, 2018</t>
+  </si>
+  <si>
+    <t>Nov 30, 2017</t>
+  </si>
+  <si>
+    <t>Sep 29, 2017</t>
+  </si>
+  <si>
+    <t>Aug 10, 2017</t>
+  </si>
+  <si>
+    <t>Jun 26, 2017</t>
+  </si>
+  <si>
+    <t>May 10, 2017</t>
+  </si>
+  <si>
+    <t>Mar 28, 2017</t>
+  </si>
+  <si>
+    <t>Jan 18, 2017</t>
+  </si>
+  <si>
+    <t>Nov 09, 2016</t>
+  </si>
+  <si>
+    <t>Sep 01, 2016</t>
+  </si>
+  <si>
+    <t>Mar 18, 2016</t>
+  </si>
+  <si>
+    <t>Feb 02, 2016</t>
+  </si>
+  <si>
+    <t>Dec 01, 2015</t>
+  </si>
+  <si>
+    <t>Nov 20, 2015</t>
+  </si>
+  <si>
+    <t>Oct 07, 2015</t>
+  </si>
+  <si>
+    <t>Sep 28, 2015</t>
+  </si>
+  <si>
+    <t>Aug 18, 2015</t>
+  </si>
+  <si>
+    <t>Jul 01, 2015</t>
+  </si>
+  <si>
+    <t>May 19, 2015</t>
+  </si>
+  <si>
+    <t>Apr 29, 2015</t>
+  </si>
+  <si>
+    <t>Mar 23, 2015</t>
+  </si>
+  <si>
+    <t>Feb 15, 2015</t>
+  </si>
+  <si>
+    <t>Jan 23, 2015</t>
+  </si>
+  <si>
+    <t>Jan 09, 2015</t>
+  </si>
+  <si>
+    <t>Nov 02, 2014</t>
+  </si>
+  <si>
+    <t>Sep 24, 2014</t>
+  </si>
+  <si>
+    <t>Aug 29, 2014</t>
+  </si>
+  <si>
+    <t>Aug 15, 2014</t>
+  </si>
+  <si>
+    <t>Jun 19, 2014</t>
+  </si>
+  <si>
+    <t>May 16, 2014</t>
+  </si>
+  <si>
+    <t>Mar 24, 2014</t>
+  </si>
+  <si>
+    <t>Feb 07, 2014</t>
+  </si>
+  <si>
+    <t>Jan 29, 2014</t>
+  </si>
+  <si>
+    <t>Sep 20, 2020</t>
+  </si>
+  <si>
+    <t>Jul 07, 2020</t>
+  </si>
+  <si>
+    <t>May 16, 2020</t>
+  </si>
+  <si>
+    <t>Mar 19, 2020</t>
+  </si>
+  <si>
+    <t>Feb 14, 2020</t>
+  </si>
+  <si>
+    <t>Dec 11, 2019</t>
+  </si>
+  <si>
+    <t>Jul 29, 2019</t>
+  </si>
+  <si>
+    <t>Feb 21, 2019</t>
+  </si>
+  <si>
+    <t>Nov 15, 2018</t>
+  </si>
+  <si>
+    <t>Sep 19, 2018</t>
+  </si>
+  <si>
+    <t>Jul 02, 2018</t>
+  </si>
+  <si>
+    <t>May 07, 2018</t>
+  </si>
+  <si>
+    <t>Aug 11, 2017</t>
+  </si>
+  <si>
+    <t>Mar 09, 2017</t>
+  </si>
+  <si>
+    <t>Nov 07, 2016</t>
+  </si>
+  <si>
+    <t>Sep 14, 2016</t>
+  </si>
+  <si>
+    <t>Jun 15, 2016</t>
+  </si>
+  <si>
+    <t>Apr 11, 2016</t>
+  </si>
+  <si>
+    <t>Feb 08, 2016</t>
+  </si>
+  <si>
+    <t>Dec 07, 2015</t>
+  </si>
+  <si>
+    <t>Oct 09, 2015</t>
+  </si>
+  <si>
+    <t>Aug 19, 2015</t>
+  </si>
+  <si>
+    <t>Jun 30, 2015</t>
+  </si>
+  <si>
+    <t>May 07, 2015</t>
+  </si>
+  <si>
+    <t>Mar 27, 2015</t>
+  </si>
+  <si>
+    <t>Jan 28, 2015</t>
+  </si>
+  <si>
+    <t>Nov 03, 2014</t>
+  </si>
+  <si>
+    <t>Sep 28, 2014</t>
+  </si>
+  <si>
+    <t>Jul 18, 2014</t>
+  </si>
+  <si>
+    <t>May 20, 2014</t>
+  </si>
+  <si>
+    <t>Mar 25, 2014</t>
+  </si>
+  <si>
+    <t>Feb 13, 2014</t>
+  </si>
+  <si>
+    <t>Dec 19, 2013</t>
+  </si>
+  <si>
+    <t>Oct 18, 2013</t>
+  </si>
+  <si>
+    <t>Jul 02, 2013</t>
+  </si>
+  <si>
+    <t>Jun 06, 2013</t>
+  </si>
+  <si>
+    <t>May 05, 2013</t>
+  </si>
+  <si>
+    <t>Mar 22, 2013</t>
+  </si>
+  <si>
+    <t>Feb 12, 2013</t>
+  </si>
+  <si>
+    <t>Jan 10, 2013</t>
+  </si>
+  <si>
+    <t>Dec 04, 2012</t>
+  </si>
+  <si>
+    <t>Nov 18, 2012</t>
+  </si>
+  <si>
+    <t>Oct 03, 2012</t>
+  </si>
+  <si>
+    <t>Sep 02, 2012</t>
+  </si>
+  <si>
+    <t>Jul 03, 2012</t>
+  </si>
+  <si>
+    <t>Jun 15, 2012</t>
+  </si>
+  <si>
+    <t>Mar 31, 2012</t>
+  </si>
+  <si>
+    <t>Feb 17, 2012</t>
+  </si>
+  <si>
+    <t>Jan 17, 2012</t>
+  </si>
+  <si>
+    <t>Nov 24, 2011</t>
+  </si>
+  <si>
+    <t>Oct 10, 2011</t>
+  </si>
+  <si>
+    <t>Sep 01, 2011</t>
+  </si>
+  <si>
+    <t>Aug 16, 2011</t>
+  </si>
+  <si>
+    <t>Jul 25, 2011</t>
+  </si>
+  <si>
+    <t>Jun 17, 2011</t>
+  </si>
+  <si>
+    <t>May 12, 2011</t>
+  </si>
+  <si>
+    <t>Apr 17, 2011</t>
+  </si>
+  <si>
+    <t>Mar 12, 2011</t>
+  </si>
+  <si>
+    <t>Feb 16, 2011</t>
+  </si>
+  <si>
+    <t>Jan 17, 2011</t>
+  </si>
+  <si>
+    <t>Dec 02, 2010</t>
+  </si>
+  <si>
+    <t>Oct 26, 2010</t>
+  </si>
+  <si>
+    <t>Aug 22, 2010</t>
+  </si>
+  <si>
+    <t>Jul 12, 2010</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1058,8 +1793,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -1075,6 +1811,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1340,2638 +2080,3628 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B329"/>
+  <dimension ref="A1:C329"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C2">
         <v>8.1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3">
         <v>8.1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C4">
         <v>7.3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5">
         <v>8.1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6">
         <v>8.1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7">
         <v>8.1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C8">
         <v>8.1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C9">
         <v>8.1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10">
         <v>8.1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11">
         <v>8.1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C12">
         <v>8.1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C13">
         <v>7.8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C14">
         <v>7.8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C15">
         <v>7.8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B16" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C16">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B17" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C17">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C18">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B19" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C19">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B20" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C20">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C21">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B22" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C22">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B23" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C23">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B24" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C24">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B25" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C25">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B26" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C26">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B27" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C27">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B28" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C28">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B29" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C29">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B30" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C30">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C31">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C32">
         <v>6.15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C33">
         <v>6.15</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C34">
         <v>6.15</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C35">
         <v>6.15</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>35</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C36">
         <v>6.15</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>36</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C37">
         <v>6.15</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>37</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C38">
         <v>6.15</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>38</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C39">
         <v>6.15</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>39</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C40">
         <v>6.15</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41">
         <v>6.15</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C42">
         <v>6.15</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C43">
         <v>6.15</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>43</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C44">
         <v>6.15</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>44</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C45">
         <v>6.15</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>45</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C46">
         <v>6.15</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>46</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C47">
         <v>6.15</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C48">
         <v>6.15</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>48</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C49">
         <v>6.15</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C50">
         <v>6.15</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C51">
         <v>7.25</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>51</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C52">
         <v>8.1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>52</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C53">
         <v>8.1</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>53</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C54">
         <v>8.1</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>54</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C55">
         <v>8.1</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>55</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C56">
         <v>8.1</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C57">
         <v>8.1</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>57</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C58">
         <v>8.1</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>58</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C59">
         <v>8.1</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>59</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C60">
         <v>8.1</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C61">
         <v>8.1</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>61</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C62">
         <v>8.1</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>62</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C63">
         <v>7.8</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>63</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C64">
         <v>7.8</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>64</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C65">
         <v>7.8</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>65</v>
       </c>
-      <c r="B66">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B66" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C66">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>66</v>
       </c>
-      <c r="B67">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B67" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C67">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>67</v>
       </c>
-      <c r="B68">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B68" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C68">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>68</v>
       </c>
-      <c r="B69">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B69" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C69">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>69</v>
       </c>
-      <c r="B70">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C70">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>70</v>
       </c>
-      <c r="B71">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B71" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C71">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>71</v>
       </c>
-      <c r="B72">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C72">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>72</v>
       </c>
-      <c r="B73">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B73" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C73">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>73</v>
       </c>
-      <c r="B74">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B74" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C74">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>74</v>
       </c>
-      <c r="B75">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B75" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C75">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>75</v>
       </c>
-      <c r="B76">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B76" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C76">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>76</v>
       </c>
-      <c r="B77">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B77" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C77">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>77</v>
       </c>
-      <c r="B78">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B78" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C78">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>78</v>
       </c>
-      <c r="B79">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B79" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C79">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>79</v>
       </c>
-      <c r="B80">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B80" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C80">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>80</v>
       </c>
-      <c r="B81">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B81" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C81">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>81</v>
       </c>
-      <c r="B82">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B82" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C82">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>82</v>
       </c>
-      <c r="B83">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B83" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C83">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
-      <c r="B84">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B84" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C84">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>84</v>
       </c>
-      <c r="B85">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B85" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C85">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>85</v>
       </c>
-      <c r="B86">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B86" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C86">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>86</v>
       </c>
-      <c r="B87">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B87" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C87">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>87</v>
       </c>
-      <c r="B88">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B88" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C88">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>88</v>
       </c>
-      <c r="B89">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B89" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C89">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>89</v>
       </c>
-      <c r="B90">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B90" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C90">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>90</v>
       </c>
-      <c r="B91">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B91" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C91">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>91</v>
       </c>
-      <c r="B92">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C92">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>92</v>
       </c>
-      <c r="B93">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B93" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C93">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>93</v>
       </c>
-      <c r="B94">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B94" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C94">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>94</v>
       </c>
-      <c r="B95">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B95" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C95">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>95</v>
       </c>
-      <c r="B96">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B96" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C96">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>96</v>
       </c>
-      <c r="B97">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C97">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>97</v>
       </c>
-      <c r="B98">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B98" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C98">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>98</v>
       </c>
-      <c r="B99">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B99" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C99">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>99</v>
       </c>
-      <c r="B100">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B100" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C100">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>100</v>
       </c>
-      <c r="B101">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B101" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C101">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>101</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C102">
         <v>7.25</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>102</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C103">
         <v>7.25</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>103</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C104">
         <v>7.25</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>104</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C105">
         <v>7.25</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>105</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C106">
         <v>7.25</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>106</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C107">
         <v>7.25</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C108">
         <v>7.25</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>108</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C109">
         <v>7.25</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>109</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C110">
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C111">
         <v>7.25</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>111</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C112">
         <v>7.45</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>112</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C113">
         <v>7.45</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>113</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C114">
         <v>7.45</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>114</v>
       </c>
-      <c r="B115">
+      <c r="B115" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C115">
         <v>7.45</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>115</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C116">
         <v>7.45</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>116</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C117">
         <v>7.45</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>117</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C118">
         <v>7.4</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>118</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C119">
         <v>7.4</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>119</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C120">
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>120</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C121">
         <v>7.2</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>121</v>
       </c>
-      <c r="B122">
+      <c r="B122" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C122">
         <v>7.2</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>122</v>
       </c>
-      <c r="B123">
+      <c r="B123" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C123">
         <v>7.2</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>123</v>
       </c>
-      <c r="B124">
+      <c r="B124" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C124">
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>124</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C125">
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>125</v>
       </c>
-      <c r="B126">
+      <c r="B126" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C126">
         <v>6.75</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>126</v>
       </c>
-      <c r="B127">
+      <c r="B127" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C127">
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>127</v>
       </c>
-      <c r="B128">
+      <c r="B128" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C128">
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>128</v>
       </c>
-      <c r="B129">
+      <c r="B129" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C129">
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>129</v>
       </c>
-      <c r="B130">
+      <c r="B130" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C130">
         <v>6.5</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>130</v>
       </c>
-      <c r="B131">
+      <c r="B131" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C131">
         <v>6.5</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>131</v>
       </c>
-      <c r="B132">
+      <c r="B132" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C132">
         <v>6.5</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>132</v>
       </c>
-      <c r="B133">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B133" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C133">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>133</v>
       </c>
-      <c r="B134">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B134" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C134">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>134</v>
       </c>
-      <c r="B135">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B135" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C135">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>135</v>
       </c>
-      <c r="B136">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B136" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C136">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>136</v>
       </c>
-      <c r="B137">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B137" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C137">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>137</v>
       </c>
-      <c r="B138">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B138" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C138">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>138</v>
       </c>
-      <c r="B139">
+      <c r="B139" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C139">
         <v>6.8</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>139</v>
       </c>
-      <c r="B140">
+      <c r="B140" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C140">
         <v>6.8</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>140</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C141">
         <v>6.8</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>141</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C142">
         <v>6.8</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>142</v>
       </c>
-      <c r="B143">
+      <c r="B143" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C143">
         <v>6.8</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>143</v>
       </c>
-      <c r="B144">
+      <c r="B144" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C144">
         <v>6.5</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>144</v>
       </c>
-      <c r="B145">
+      <c r="B145" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C145">
         <v>6.5</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>145</v>
       </c>
-      <c r="B146">
+      <c r="B146" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C146">
         <v>6.5</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>146</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C147">
         <v>6.8</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>147</v>
       </c>
-      <c r="B148">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C148">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>148</v>
       </c>
-      <c r="B149">
+      <c r="B149" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C149">
         <v>6.1</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>149</v>
       </c>
-      <c r="B150">
+      <c r="B150" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C150">
         <v>6.1</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>150</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C151">
         <v>6.1</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>151</v>
       </c>
-      <c r="B152">
+      <c r="B152" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C152">
         <v>6.1</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>152</v>
       </c>
-      <c r="B153">
+      <c r="B153" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C153">
         <v>6.1</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>153</v>
       </c>
-      <c r="B154">
+      <c r="B154" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C154">
         <v>6.1</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>154</v>
       </c>
-      <c r="B155">
+      <c r="B155" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C155">
         <v>6.1</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>155</v>
       </c>
-      <c r="B156">
+      <c r="B156" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C156">
         <v>6.1</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>156</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C157">
         <v>6.1</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>157</v>
       </c>
-      <c r="B158">
+      <c r="B158" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C158">
         <v>6.1</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>158</v>
       </c>
-      <c r="B159">
+      <c r="B159" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C159">
         <v>6.1</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>159</v>
       </c>
-      <c r="B160">
+      <c r="B160" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C160">
         <v>6.1</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>160</v>
       </c>
-      <c r="B161">
+      <c r="B161" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C161">
         <v>6.1</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>161</v>
       </c>
-      <c r="B162">
+      <c r="B162" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C162">
         <v>6.1</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>162</v>
       </c>
-      <c r="B163">
+      <c r="B163" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C163">
         <v>6.1</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>163</v>
       </c>
-      <c r="B164">
+      <c r="B164" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C164">
         <v>6.1</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>164</v>
       </c>
-      <c r="B165">
+      <c r="B165" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C165">
         <v>5.6999999999999993</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>165</v>
       </c>
-      <c r="B166">
+      <c r="B166" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C166">
         <v>6.1</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>166</v>
       </c>
-      <c r="B167">
+      <c r="B167" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C167">
         <v>6.55</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>167</v>
       </c>
-      <c r="B168">
+      <c r="B168" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C168">
         <v>6.1</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>168</v>
       </c>
-      <c r="B169">
+      <c r="B169" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C169">
         <v>6.1</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>169</v>
       </c>
-      <c r="B170">
+      <c r="B170" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C170">
         <v>6.1</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>170</v>
       </c>
-      <c r="B171">
+      <c r="B171" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C171">
         <v>6.1</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>171</v>
       </c>
-      <c r="B172">
+      <c r="B172" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C172">
         <v>6.1</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>172</v>
       </c>
-      <c r="B173">
+      <c r="B173" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C173">
         <v>6.1</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>173</v>
       </c>
-      <c r="B174">
+      <c r="B174" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C174">
         <v>6.1</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>174</v>
       </c>
-      <c r="B175">
+      <c r="B175" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C175">
         <v>6.1</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>175</v>
       </c>
-      <c r="B176">
+      <c r="B176" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C176">
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>176</v>
       </c>
-      <c r="B177">
+      <c r="B177" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C177">
         <v>6.1</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>177</v>
       </c>
-      <c r="B178">
+      <c r="B178" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C178">
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>178</v>
       </c>
-      <c r="B179">
+      <c r="B179" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C179">
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>179</v>
       </c>
-      <c r="B180">
+      <c r="B180" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C180">
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>180</v>
       </c>
-      <c r="B181">
+      <c r="B181" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C181">
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>181</v>
       </c>
-      <c r="B182">
+      <c r="B182" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C182">
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>182</v>
       </c>
-      <c r="B183">
+      <c r="B183" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C183">
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>183</v>
       </c>
-      <c r="B184">
+      <c r="B184" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C184">
         <v>6.55</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>184</v>
       </c>
-      <c r="B185">
+      <c r="B185" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C185">
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>185</v>
       </c>
-      <c r="B186">
+      <c r="B186" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C186">
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>186</v>
       </c>
-      <c r="B187">
+      <c r="B187" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C187">
         <v>6.1</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>187</v>
       </c>
-      <c r="B188">
+      <c r="B188" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C188">
         <v>6.1</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>188</v>
       </c>
-      <c r="B189">
+      <c r="B189" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C189">
         <v>6.1</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>189</v>
       </c>
-      <c r="B190">
+      <c r="B190" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C190">
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>190</v>
       </c>
-      <c r="B191">
+      <c r="B191" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C191">
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>191</v>
       </c>
-      <c r="B192">
+      <c r="B192" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C192">
         <v>5.9</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>192</v>
       </c>
-      <c r="B193">
+      <c r="B193" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C193">
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>193</v>
       </c>
-      <c r="B194">
+      <c r="B194" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C194">
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>194</v>
       </c>
-      <c r="B195">
+      <c r="B195" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C195">
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>195</v>
       </c>
-      <c r="B196">
+      <c r="B196" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C196">
         <v>6</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>196</v>
       </c>
-      <c r="B197">
+      <c r="B197" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C197">
         <v>6</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>197</v>
       </c>
-      <c r="B198">
+      <c r="B198" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C198">
         <v>6</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>198</v>
       </c>
-      <c r="B199">
+      <c r="B199" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C199">
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>199</v>
       </c>
-      <c r="B200">
+      <c r="B200" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C200">
         <v>6</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>200</v>
       </c>
-      <c r="B201">
+      <c r="B201" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C201">
         <v>6</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>201</v>
       </c>
-      <c r="B202">
+      <c r="B202" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C202">
         <v>6</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>202</v>
       </c>
-      <c r="B203">
+      <c r="B203" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C203">
         <v>6</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>203</v>
       </c>
-      <c r="B204">
+      <c r="B204" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C204">
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>204</v>
       </c>
-      <c r="B205">
+      <c r="B205" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C205">
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>205</v>
       </c>
-      <c r="B206">
+      <c r="B206" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C206">
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>206</v>
       </c>
-      <c r="B207">
+      <c r="B207" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C207">
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>207</v>
       </c>
-      <c r="B208">
+      <c r="B208" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C208">
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>208</v>
       </c>
-      <c r="B209">
+      <c r="B209" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C209">
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>209</v>
       </c>
-      <c r="B210">
+      <c r="B210" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C210">
         <v>6.1</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>210</v>
       </c>
-      <c r="B211">
+      <c r="B211" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C211">
         <v>6.1</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>211</v>
       </c>
-      <c r="B212">
+      <c r="B212" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C212">
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>212</v>
       </c>
-      <c r="B213">
+      <c r="B213" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C213">
         <v>6</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>213</v>
       </c>
-      <c r="B214">
+      <c r="B214" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C214">
         <v>6</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>214</v>
       </c>
-      <c r="B215">
+      <c r="B215" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C215">
         <v>6</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>215</v>
       </c>
-      <c r="B216">
+      <c r="B216" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C216">
         <v>7.2</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>216</v>
       </c>
-      <c r="B217">
+      <c r="B217" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C217">
         <v>6.45</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>217</v>
       </c>
-      <c r="B218">
+      <c r="B218" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C218">
         <v>6.45</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>218</v>
       </c>
-      <c r="B219">
+      <c r="B219" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C219">
         <v>6.75</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>219</v>
       </c>
-      <c r="B220">
+      <c r="B220" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C220">
         <v>6.75</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>220</v>
       </c>
-      <c r="B221">
+      <c r="B221" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C221">
         <v>6.75</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>221</v>
       </c>
-      <c r="B222">
+      <c r="B222" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C222">
         <v>6.75</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>222</v>
       </c>
-      <c r="B223">
+      <c r="B223" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C223">
         <v>6.75</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>223</v>
       </c>
-      <c r="B224">
+      <c r="B224" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C224">
         <v>6.75</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>224</v>
       </c>
-      <c r="B225">
+      <c r="B225" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C225">
         <v>6.75</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>225</v>
       </c>
-      <c r="B226">
+      <c r="B226" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C226">
         <v>6.75</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>226</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C227">
         <v>6.75</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>227</v>
       </c>
-      <c r="B228">
+      <c r="B228" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C228">
         <v>6.5</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>228</v>
       </c>
-      <c r="B229">
+      <c r="B229" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C229">
         <v>6.5</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>229</v>
       </c>
-      <c r="B230">
+      <c r="B230" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C230">
         <v>6.5</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>230</v>
       </c>
-      <c r="B231">
+      <c r="B231" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C231">
         <v>6.5</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>231</v>
       </c>
-      <c r="B232">
+      <c r="B232" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C232">
         <v>6.5</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>232</v>
       </c>
-      <c r="B233">
+      <c r="B233" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C233">
         <v>6.5</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>233</v>
       </c>
-      <c r="B234">
+      <c r="B234" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C234">
         <v>6.5</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>234</v>
       </c>
-      <c r="B235">
+      <c r="B235" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C235">
         <v>6.5</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>235</v>
       </c>
-      <c r="B236">
+      <c r="B236" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C236">
         <v>6.5</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>236</v>
       </c>
-      <c r="B237">
+      <c r="B237" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C237">
         <v>6.5</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>237</v>
       </c>
-      <c r="B238">
+      <c r="B238" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C238">
         <v>6.5</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>238</v>
       </c>
-      <c r="B239">
+      <c r="B239" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C239">
         <v>6.5</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>239</v>
       </c>
-      <c r="B240">
+      <c r="B240" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C240">
         <v>6.5</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>240</v>
       </c>
-      <c r="B241">
+      <c r="B241" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C241">
         <v>6.5</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>240</v>
       </c>
-      <c r="B242">
+      <c r="B242" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C242">
         <v>6.5</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>241</v>
       </c>
-      <c r="B243">
+      <c r="B243" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C243">
         <v>6.5</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>242</v>
       </c>
-      <c r="B244">
+      <c r="B244" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C244">
         <v>6.5</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>243</v>
       </c>
-      <c r="B245">
+      <c r="B245" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C245">
         <v>6.5</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>244</v>
       </c>
-      <c r="B246">
+      <c r="B246" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C246">
         <v>6.5</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>245</v>
       </c>
-      <c r="B247">
+      <c r="B247" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C247">
         <v>6.5</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>246</v>
       </c>
-      <c r="B248">
+      <c r="B248" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C248">
         <v>6.5</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>247</v>
       </c>
-      <c r="B249">
+      <c r="B249" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C249">
         <v>6.5</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>248</v>
       </c>
-      <c r="B250">
+      <c r="B250" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C250">
         <v>6.5</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>249</v>
       </c>
-      <c r="B251">
+      <c r="B251" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C251">
         <v>6.5</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>250</v>
       </c>
-      <c r="B252">
+      <c r="B252" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C252">
         <v>6.5</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>251</v>
       </c>
-      <c r="B253">
+      <c r="B253" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C253">
         <v>6.5</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>252</v>
       </c>
-      <c r="B254">
+      <c r="B254" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C254">
         <v>6.5</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>253</v>
       </c>
-      <c r="B255">
+      <c r="B255" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C255">
         <v>6.2</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>254</v>
       </c>
-      <c r="B256">
+      <c r="B256" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C256">
         <v>6.2</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>255</v>
       </c>
-      <c r="B257">
+      <c r="B257" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C257">
         <v>6.45</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>256</v>
       </c>
-      <c r="B258">
+      <c r="B258" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C258">
         <v>6.45</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>257</v>
       </c>
-      <c r="B259">
+      <c r="B259" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C259">
         <v>6.45</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>258</v>
       </c>
-      <c r="B260">
+      <c r="B260" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C260">
         <v>6.45</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>259</v>
       </c>
-      <c r="B261">
+      <c r="B261" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C261">
         <v>6.45</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>260</v>
       </c>
-      <c r="B262">
+      <c r="B262" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C262">
         <v>5.9</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>261</v>
       </c>
-      <c r="B263">
+      <c r="B263" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C263">
         <v>7.2</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>262</v>
       </c>
-      <c r="B264">
+      <c r="B264" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C264">
         <v>7.2</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>263</v>
       </c>
-      <c r="B265">
+      <c r="B265" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C265">
         <v>6.45</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>264</v>
       </c>
-      <c r="B266">
+      <c r="B266" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C266">
         <v>6.45</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>265</v>
       </c>
-      <c r="B267">
+      <c r="B267" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C267">
         <v>6.45</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>266</v>
       </c>
-      <c r="B268">
+      <c r="B268" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C268">
         <v>5.9</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>267</v>
       </c>
-      <c r="B269">
+      <c r="B269" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C269">
         <v>5.9</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>268</v>
       </c>
-      <c r="B270">
+      <c r="B270" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C270">
         <v>5.9</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>269</v>
       </c>
-      <c r="B271">
+      <c r="B271" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C271">
         <v>5.9</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>270</v>
       </c>
-      <c r="B272">
+      <c r="B272" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C272">
         <v>5.9</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>271</v>
       </c>
-      <c r="B273">
+      <c r="B273" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C273">
         <v>5.9</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>272</v>
       </c>
-      <c r="B274">
+      <c r="B274" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C274">
         <v>5.9</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>273</v>
       </c>
-      <c r="B275">
+      <c r="B275" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C275">
         <v>5.9</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>274</v>
       </c>
-      <c r="B276">
+      <c r="B276" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C276">
         <v>5.9</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>275</v>
       </c>
-      <c r="B277">
+      <c r="B277" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C277">
         <v>5.9</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>276</v>
       </c>
-      <c r="B278">
+      <c r="B278" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C278">
         <v>5.9</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>277</v>
       </c>
-      <c r="B279">
+      <c r="B279" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C279">
         <v>5.9</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>278</v>
       </c>
-      <c r="B280">
+      <c r="B280" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C280">
         <v>5.9</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>279</v>
       </c>
-      <c r="B281">
+      <c r="B281" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C281">
         <v>5.9</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>280</v>
       </c>
-      <c r="B282">
+      <c r="B282" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C282">
         <v>5.9</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>281</v>
       </c>
-      <c r="B283">
+      <c r="B283" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C283">
         <v>5.9</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>282</v>
       </c>
-      <c r="B284">
+      <c r="B284" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C284">
         <v>5.9</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>283</v>
       </c>
-      <c r="B285">
+      <c r="B285" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C285">
         <v>5.9</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>284</v>
       </c>
-      <c r="B286">
+      <c r="B286" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C286">
         <v>5.9</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>285</v>
       </c>
-      <c r="B287">
+      <c r="B287" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C287">
         <v>5.9</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>286</v>
       </c>
-      <c r="B288">
+      <c r="B288" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C288">
         <v>5.9</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>287</v>
       </c>
-      <c r="B289">
+      <c r="B289" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C289">
         <v>5.9</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>288</v>
       </c>
-      <c r="B290">
+      <c r="B290" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C290">
         <v>5.9</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>289</v>
       </c>
-      <c r="B291">
+      <c r="B291" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C291">
         <v>5.9</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>290</v>
       </c>
-      <c r="B292">
+      <c r="B292" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C292">
         <v>5.9</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>291</v>
       </c>
-      <c r="B293">
+      <c r="B293" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C293">
         <v>5.9</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>292</v>
       </c>
-      <c r="B294">
+      <c r="B294" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C294">
         <v>5.9</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>293</v>
       </c>
-      <c r="B295">
+      <c r="B295" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C295">
         <v>5.9</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>294</v>
       </c>
-      <c r="B296">
+      <c r="B296" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C296">
         <v>5.9</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>295</v>
       </c>
-      <c r="B297">
+      <c r="B297" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C297">
         <v>5.9</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>296</v>
       </c>
-      <c r="B298">
+      <c r="B298" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C298">
         <v>5.9</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>297</v>
       </c>
-      <c r="B299">
+      <c r="B299" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C299">
         <v>5.9</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>298</v>
       </c>
-      <c r="B300">
+      <c r="B300" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C300">
         <v>5.9</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>299</v>
       </c>
-      <c r="B301">
+      <c r="B301" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C301">
         <v>5.9</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>300</v>
       </c>
-      <c r="B302">
+      <c r="B302" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C302">
         <v>5.9</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>301</v>
       </c>
-      <c r="B303">
+      <c r="B303" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C303">
         <v>5.9</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>302</v>
       </c>
-      <c r="B304">
+      <c r="B304" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C304">
         <v>5.9</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>303</v>
       </c>
-      <c r="B305">
+      <c r="B305" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C305">
         <v>5.9</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>304</v>
       </c>
-      <c r="B306">
+      <c r="B306" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C306">
         <v>6.2</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>305</v>
       </c>
-      <c r="B307">
+      <c r="B307" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C307">
         <v>6.2</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>306</v>
       </c>
-      <c r="B308">
+      <c r="B308" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C308">
         <v>6.2</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>307</v>
       </c>
-      <c r="B309">
+      <c r="B309" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C309">
         <v>6.2</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>308</v>
       </c>
-      <c r="B310">
+      <c r="B310" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C310">
         <v>6.2</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>309</v>
       </c>
-      <c r="B311">
+      <c r="B311" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C311">
         <v>6.2</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>310</v>
       </c>
-      <c r="B312">
+      <c r="B312" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C312">
         <v>5.9</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>311</v>
       </c>
-      <c r="B313">
+      <c r="B313" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C313">
         <v>5.9</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>312</v>
       </c>
-      <c r="B314">
+      <c r="B314" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C314">
         <v>5.9</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>313</v>
       </c>
-      <c r="B315">
+      <c r="B315" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C315">
         <v>5.9</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>314</v>
       </c>
-      <c r="B316">
+      <c r="B316" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C316">
         <v>6.2</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>315</v>
       </c>
-      <c r="B317">
+      <c r="B317" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C317">
         <v>6.2</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>316</v>
       </c>
-      <c r="B318">
+      <c r="B318" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C318">
         <v>6.2</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>317</v>
       </c>
-      <c r="B319">
+      <c r="B319" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C319">
         <v>6.2</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>318</v>
       </c>
-      <c r="B320">
+      <c r="B320" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C320">
         <v>6.2</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>319</v>
       </c>
-      <c r="B321">
+      <c r="B321" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C321">
         <v>6.2</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>320</v>
       </c>
-      <c r="B322">
+      <c r="B322" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C322">
         <v>6.2</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>321</v>
       </c>
-      <c r="B323">
+      <c r="B323" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C323">
         <v>6.2</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>322</v>
       </c>
-      <c r="B324">
+      <c r="B324" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C324">
         <v>6.2</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>323</v>
       </c>
-      <c r="B325">
+      <c r="B325" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C325">
         <v>6.2</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>324</v>
       </c>
-      <c r="B326">
+      <c r="B326" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C326">
         <v>6.2</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>325</v>
       </c>
-      <c r="B327">
+      <c r="B327" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C327">
         <v>6.2</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>326</v>
       </c>
-      <c r="B328">
+      <c r="B328" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C328">
         <v>6.2</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>327</v>
       </c>
-      <c r="B329">
+      <c r="B329" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C329">
         <v>6.2</v>
       </c>
     </row>
